--- a/artfynd/A 32064-2022 artfynd.xlsx
+++ b/artfynd/A 32064-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 32064-2022 artfynd.xlsx
+++ b/artfynd/A 32064-2022 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112354257</v>
+        <v>112352526</v>
       </c>
       <c r="B2" t="n">
-        <v>90328</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87146</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>232138</v>
+        <v>3762</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>675093</v>
+        <v>675094</v>
       </c>
       <c r="R2" t="n">
-        <v>6687285</v>
+        <v>6687286</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -788,37 +783,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112352526</v>
+        <v>112354257</v>
       </c>
       <c r="B3" t="n">
-        <v>85265</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92688</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3762</v>
+        <v>232138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Gul lammticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Albatrellus citrinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Ryman</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -829,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>675093</v>
+        <v>675094</v>
       </c>
       <c r="R3" t="n">
-        <v>6687285</v>
+        <v>6687286</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 32064-2022 artfynd.xlsx
+++ b/artfynd/A 32064-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112352526</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,8 +898,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112354257</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>